--- a/12625080.xlsx
+++ b/12625080.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\91823\OneDrive\Desktop\12625080\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e149e35e993224e1/Desktop/Demo/CAP-776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C93A1E68-2BC2-4AA1-AA42-5607C2755F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{C93A1E68-2BC2-4AA1-AA42-5607C2755F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08DB65F3-7BDD-46C2-8678-937B3B663721}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -230,6 +230,9 @@
   </si>
   <si>
     <t>get compliment on my content creation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">got sick </t>
   </si>
 </sst>
 </file>
@@ -1193,48 +1196,94 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="10" t="str">
+      <c r="A10" s="8">
+        <v>46256</v>
+      </c>
+      <c r="B10" s="14">
+        <v>440</v>
+      </c>
+      <c r="C10" s="14">
+        <v>10</v>
+      </c>
+      <c r="D10" s="14">
+        <v>100</v>
+      </c>
+      <c r="E10" s="14">
+        <v>200</v>
+      </c>
+      <c r="F10" s="14">
+        <v>0</v>
+      </c>
+      <c r="G10" s="14">
+        <v>0</v>
+      </c>
+      <c r="H10" s="14">
+        <v>320</v>
+      </c>
+      <c r="I10" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="10" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J10" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
+        <v>370</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N10" s="17"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="10" t="str">
+      <c r="A11" s="8">
+        <v>46257</v>
+      </c>
+      <c r="B11" s="14">
+        <v>450</v>
+      </c>
+      <c r="C11" s="14">
+        <v>0</v>
+      </c>
+      <c r="D11" s="14">
+        <v>120</v>
+      </c>
+      <c r="E11" s="14">
+        <v>220</v>
+      </c>
+      <c r="F11" s="14">
+        <v>0</v>
+      </c>
+      <c r="G11" s="14">
+        <v>0</v>
+      </c>
+      <c r="H11" s="14">
+        <v>350</v>
+      </c>
+      <c r="I11" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="10" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J11" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
+        <v>300</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="13"/>

--- a/12625080.xlsx
+++ b/12625080.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e149e35e993224e1/Desktop/Demo/CAP-776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{C93A1E68-2BC2-4AA1-AA42-5607C2755F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08DB65F3-7BDD-46C2-8678-937B3B663721}"/>
+  <xr:revisionPtr revIDLastSave="80" documentId="13_ncr:1_{C93A1E68-2BC2-4AA1-AA42-5607C2755F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D65F7A7-8BDC-4565-B19A-BCC34D04614D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -233,6 +233,15 @@
   </si>
   <si>
     <t xml:space="preserve">got sick </t>
+  </si>
+  <si>
+    <t>very tired</t>
+  </si>
+  <si>
+    <t>loved spending time with friends.</t>
+  </si>
+  <si>
+    <t>spend day in sleeping</t>
   </si>
 </sst>
 </file>
@@ -513,6 +522,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1286,92 +1299,186 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="10" t="str">
+      <c r="A12" s="8">
+        <v>46258</v>
+      </c>
+      <c r="B12" s="14">
+        <v>420</v>
+      </c>
+      <c r="C12" s="14">
+        <v>20</v>
+      </c>
+      <c r="D12" s="14">
+        <v>100</v>
+      </c>
+      <c r="E12" s="14">
+        <v>100</v>
+      </c>
+      <c r="F12" s="14">
+        <v>200</v>
+      </c>
+      <c r="G12" s="14">
+        <v>4</v>
+      </c>
+      <c r="H12" s="14">
+        <v>380</v>
+      </c>
+      <c r="I12" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="10" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J12" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
+        <v>220</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N12" s="17"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="10" t="str">
+      <c r="A13" s="8">
+        <v>46259</v>
+      </c>
+      <c r="B13" s="14">
+        <v>400</v>
+      </c>
+      <c r="C13" s="14">
+        <v>0</v>
+      </c>
+      <c r="D13" s="14">
+        <v>80</v>
+      </c>
+      <c r="E13" s="14">
+        <v>100</v>
+      </c>
+      <c r="F13" s="14">
+        <v>350</v>
+      </c>
+      <c r="G13" s="14">
+        <v>7</v>
+      </c>
+      <c r="H13" s="14">
+        <v>220</v>
+      </c>
+      <c r="I13" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="10" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J13" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+        <v>290</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="10" t="str">
+      <c r="A14" s="8">
+        <v>46260</v>
+      </c>
+      <c r="B14" s="14">
+        <v>460</v>
+      </c>
+      <c r="C14" s="14">
+        <v>30</v>
+      </c>
+      <c r="D14" s="14">
+        <v>80</v>
+      </c>
+      <c r="E14" s="14">
+        <v>0</v>
+      </c>
+      <c r="F14" s="14">
+        <v>350</v>
+      </c>
+      <c r="G14" s="14">
+        <v>7</v>
+      </c>
+      <c r="H14" s="14">
+        <v>190</v>
+      </c>
+      <c r="I14" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="10" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J14" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="10" t="str">
+        <v>330</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="8">
+        <v>46261</v>
+      </c>
+      <c r="B15" s="14">
+        <v>380</v>
+      </c>
+      <c r="C15" s="14">
+        <v>20</v>
+      </c>
+      <c r="D15" s="14">
+        <v>150</v>
+      </c>
+      <c r="E15" s="14">
+        <v>60</v>
+      </c>
+      <c r="F15" s="14">
+        <v>200</v>
+      </c>
+      <c r="G15" s="14">
+        <v>4</v>
+      </c>
+      <c r="H15" s="14">
+        <v>340</v>
+      </c>
+      <c r="I15" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="10" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J15" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>290</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="13"/>
@@ -1448,7 +1555,7 @@
       <c r="F19" s="14"/>
       <c r="G19" s="14"/>
       <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="I19" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1470,7 +1577,7 @@
       <c r="F20" s="14"/>
       <c r="G20" s="14"/>
       <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="I20" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1492,11 +1599,11 @@
       <c r="F21" s="14"/>
       <c r="G21" s="14"/>
       <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="I21" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J21" s="15" t="str">
+      <c r="J21" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -1514,11 +1621,11 @@
       <c r="F22" s="14"/>
       <c r="G22" s="14"/>
       <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="I22" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J22" s="15" t="str">
+      <c r="J22" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>

--- a/12625080.xlsx
+++ b/12625080.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e149e35e993224e1/Desktop/Demo/CAP-776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="80" documentId="13_ncr:1_{C93A1E68-2BC2-4AA1-AA42-5607C2755F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D65F7A7-8BDC-4565-B19A-BCC34D04614D}"/>
+  <xr:revisionPtr revIDLastSave="96" documentId="13_ncr:1_{C93A1E68-2BC2-4AA1-AA42-5607C2755F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D06FF31D-F43F-464D-BCC4-961EC0B0953C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -242,6 +242,9 @@
   </si>
   <si>
     <t>spend day in sleeping</t>
+  </si>
+  <si>
+    <t>feeling bored.</t>
   </si>
 </sst>
 </file>
@@ -1481,26 +1484,50 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="10" t="str">
+      <c r="A16" s="8">
+        <v>46262</v>
+      </c>
+      <c r="B16" s="14">
+        <v>420</v>
+      </c>
+      <c r="C16" s="14">
+        <v>20</v>
+      </c>
+      <c r="D16" s="14">
+        <v>60</v>
+      </c>
+      <c r="E16" s="14">
+        <v>60</v>
+      </c>
+      <c r="F16" s="14">
+        <v>250</v>
+      </c>
+      <c r="G16" s="14">
+        <v>5</v>
+      </c>
+      <c r="H16" s="14">
+        <v>300</v>
+      </c>
+      <c r="I16" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="10" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J16" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+        <v>330</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="13"/>

--- a/12625080.xlsx
+++ b/12625080.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e149e35e993224e1/Desktop/Demo/CAP-776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="96" documentId="13_ncr:1_{C93A1E68-2BC2-4AA1-AA42-5607C2755F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D06FF31D-F43F-464D-BCC4-961EC0B0953C}"/>
+  <xr:revisionPtr revIDLastSave="131" documentId="13_ncr:1_{C93A1E68-2BC2-4AA1-AA42-5607C2755F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94F42ED4-BA87-4EC7-A7FB-757E7442FDB5}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -245,6 +245,15 @@
   </si>
   <si>
     <t>feeling bored.</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>went out with friends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">need to do hard work </t>
   </si>
 </sst>
 </file>
@@ -1530,70 +1539,140 @@
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="10" t="str">
+      <c r="A17" s="8">
+        <v>46263</v>
+      </c>
+      <c r="B17" s="14">
+        <v>450</v>
+      </c>
+      <c r="C17" s="14">
+        <v>30</v>
+      </c>
+      <c r="D17" s="14">
+        <v>60</v>
+      </c>
+      <c r="E17" s="14">
+        <v>60</v>
+      </c>
+      <c r="F17" s="14">
+        <v>0</v>
+      </c>
+      <c r="G17" s="14">
+        <v>0</v>
+      </c>
+      <c r="H17" s="14">
+        <v>350</v>
+      </c>
+      <c r="I17" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="10" t="str">
+        <v>950</v>
+      </c>
+      <c r="J17" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
+        <v>490</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N17" s="17"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="10" t="str">
+      <c r="A18" s="8">
+        <v>46264</v>
+      </c>
+      <c r="B18" s="14">
+        <v>460</v>
+      </c>
+      <c r="C18" s="14">
+        <v>30</v>
+      </c>
+      <c r="D18" s="14">
+        <v>60</v>
+      </c>
+      <c r="E18" s="14">
+        <v>0</v>
+      </c>
+      <c r="F18" s="14">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14">
+        <v>0</v>
+      </c>
+      <c r="H18" s="14">
+        <v>400</v>
+      </c>
+      <c r="I18" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="10" t="str">
+        <v>950</v>
+      </c>
+      <c r="J18" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>490</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="10" t="str">
+      <c r="A19" s="8">
+        <v>46265</v>
+      </c>
+      <c r="B19" s="14">
+        <v>480</v>
+      </c>
+      <c r="C19" s="14">
+        <v>0</v>
+      </c>
+      <c r="D19" s="14">
+        <v>80</v>
+      </c>
+      <c r="E19" s="14">
+        <v>60</v>
+      </c>
+      <c r="F19" s="14">
+        <v>200</v>
+      </c>
+      <c r="G19" s="14">
+        <v>4</v>
+      </c>
+      <c r="H19" s="14">
+        <v>320</v>
+      </c>
+      <c r="I19" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="10" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J19" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>300</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="13"/>

--- a/12625080.xlsx
+++ b/12625080.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e149e35e993224e1/Desktop/Demo/CAP-776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="131" documentId="13_ncr:1_{C93A1E68-2BC2-4AA1-AA42-5607C2755F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94F42ED4-BA87-4EC7-A7FB-757E7442FDB5}"/>
+  <xr:revisionPtr revIDLastSave="167" documentId="13_ncr:1_{C93A1E68-2BC2-4AA1-AA42-5607C2755F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC5C51B7-CDBA-4F11-BFA1-EF89225C1F07}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
     <sheet name="Daily Log" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -255,6 +256,12 @@
   <si>
     <t xml:space="preserve">need to do hard work </t>
   </si>
+  <si>
+    <t>totally exhausted</t>
+  </si>
+  <si>
+    <t>unable to prepare completely for my CA</t>
+  </si>
 </sst>
 </file>
 
@@ -435,7 +442,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1675,48 +1684,96 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="10" t="str">
+      <c r="A20" s="8">
+        <v>46266</v>
+      </c>
+      <c r="B20" s="14">
+        <v>350</v>
+      </c>
+      <c r="C20" s="14">
+        <v>0</v>
+      </c>
+      <c r="D20" s="14">
+        <v>100</v>
+      </c>
+      <c r="E20" s="14">
+        <v>60</v>
+      </c>
+      <c r="F20" s="14">
+        <v>350</v>
+      </c>
+      <c r="G20" s="14">
+        <v>7</v>
+      </c>
+      <c r="H20" s="14">
+        <v>270</v>
+      </c>
+      <c r="I20" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="10" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J20" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="10" t="str">
+        <v>310</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="8">
+        <v>46267</v>
+      </c>
+      <c r="B21" s="14">
+        <v>420</v>
+      </c>
+      <c r="C21" s="14">
+        <v>0</v>
+      </c>
+      <c r="D21" s="14">
+        <v>120</v>
+      </c>
+      <c r="E21" s="14">
+        <v>60</v>
+      </c>
+      <c r="F21" s="14">
+        <v>350</v>
+      </c>
+      <c r="G21" s="14">
+        <v>7</v>
+      </c>
+      <c r="H21" s="14">
+        <v>250</v>
+      </c>
+      <c r="I21" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="10" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J21" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>240</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>
@@ -1749,11 +1806,11 @@
       <c r="F23" s="14"/>
       <c r="G23" s="14"/>
       <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="I23" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J23" s="15" t="str">
+      <c r="J23" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -1771,11 +1828,11 @@
       <c r="F24" s="14"/>
       <c r="G24" s="14"/>
       <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="I24" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J24" s="15" t="str">
+      <c r="J24" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -1793,11 +1850,11 @@
       <c r="F25" s="14"/>
       <c r="G25" s="14"/>
       <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="I25" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J25" s="15" t="str">
+      <c r="J25" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -10109,4 +10166,13 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6050F5DF-4D96-4ED2-A331-BEF946A2370E}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/12625080.xlsx
+++ b/12625080.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e149e35e993224e1/Desktop/Demo/CAP-776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="167" documentId="13_ncr:1_{C93A1E68-2BC2-4AA1-AA42-5607C2755F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC5C51B7-CDBA-4F11-BFA1-EF89225C1F07}"/>
+  <xr:revisionPtr revIDLastSave="181" documentId="13_ncr:1_{C93A1E68-2BC2-4AA1-AA42-5607C2755F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD06EEAF-8C52-412D-BA0D-A9909CBB9049}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -261,6 +261,9 @@
   </si>
   <si>
     <t>unable to prepare completely for my CA</t>
+  </si>
+  <si>
+    <t>need to focus on time management</t>
   </si>
 </sst>
 </file>
@@ -1775,27 +1778,51 @@
         <v>74</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="10" t="str">
+    <row r="22" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="8">
+        <v>46268</v>
+      </c>
+      <c r="B22" s="14">
+        <v>450</v>
+      </c>
+      <c r="C22" s="14">
+        <v>0</v>
+      </c>
+      <c r="D22" s="14">
+        <v>80</v>
+      </c>
+      <c r="E22" s="14">
+        <v>70</v>
+      </c>
+      <c r="F22" s="14">
+        <v>200</v>
+      </c>
+      <c r="G22" s="14">
+        <v>4</v>
+      </c>
+      <c r="H22" s="14">
+        <v>240</v>
+      </c>
+      <c r="I22" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="10" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J22" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>400</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="13"/>

--- a/12625080.xlsx
+++ b/12625080.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e149e35e993224e1/Desktop/Demo/CAP-776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="181" documentId="13_ncr:1_{C93A1E68-2BC2-4AA1-AA42-5607C2755F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD06EEAF-8C52-412D-BA0D-A9909CBB9049}"/>
+  <xr:revisionPtr revIDLastSave="195" documentId="13_ncr:1_{C93A1E68-2BC2-4AA1-AA42-5607C2755F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84D46E96-4AC8-460D-A205-C7A1087DCFBA}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1825,25 +1825,47 @@
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="10" t="str">
+      <c r="A23" s="8">
+        <v>46269</v>
+      </c>
+      <c r="B23" s="14">
+        <v>360</v>
+      </c>
+      <c r="C23" s="14">
+        <v>0</v>
+      </c>
+      <c r="D23" s="14">
+        <v>120</v>
+      </c>
+      <c r="E23" s="14">
+        <v>90</v>
+      </c>
+      <c r="F23" s="14">
+        <v>250</v>
+      </c>
+      <c r="G23" s="14">
+        <v>5</v>
+      </c>
+      <c r="H23" s="14">
+        <v>320</v>
+      </c>
+      <c r="I23" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="10" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J23" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
+        <v>300</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>60</v>
+      </c>
       <c r="N23" s="17"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
